--- a/output/pdf_financials_xlsx/DRX.xlsx
+++ b/output/pdf_financials_xlsx/DRX.xlsx
@@ -5004,28 +5004,28 @@
         <v>5.631</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>5.703</v>
+        <v>5.551</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>5.337</v>
+        <v>5.31</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>13.513</v>
+        <v>13.51</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>17.086</v>
+        <v>15.971</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>18.224</v>
+        <v>17.772</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>30.105</v>
+        <v>16.585</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>41.787</v>
+        <v>29.308</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>34.988</v>
+        <v>16.857</v>
       </c>
       <c r="L75" s="1" t="inlineStr">
         <is>
@@ -5033,22 +5033,22 @@
         </is>
       </c>
       <c r="M75" s="3" t="n">
-        <v>60.144</v>
+        <v>34.562</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>49.032</v>
+        <v>34.421</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>86.523</v>
+        <v>39.985</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>102.436</v>
+        <v>55.441</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>76.193</v>
+        <v>50.236</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>82.495</v>
+        <v>58.13</v>
       </c>
     </row>
     <row r="76">
@@ -10151,7 +10151,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CurrentLiabilities</t>
+          <t>OtherCurrentLiabilities</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CurrentLiabilities</t>
+          <t>OtherCurrentLiabilities</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -15104,7 +15104,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CurrentLiabilities</t>
+          <t>OtherCurrentLiabilities</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -17993,7 +17993,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>CurrentLiabilities</t>
+          <t>OtherCurrentLiabilities</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -19104,7 +19104,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>CurrentLiabilities</t>
+          <t>OtherCurrentLiabilities</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -21956,7 +21956,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>CurrentLiabilities</t>
+          <t>OtherCurrentLiabilities</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -25428,7 +25428,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>CurrentLiabilities</t>
+          <t>OtherCurrentLiabilities</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">

--- a/output/pdf_financials_xlsx/DRX.xlsx
+++ b/output/pdf_financials_xlsx/DRX.xlsx
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.489</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.099</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>13.272</v>
+        <v>13.761</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>8.287000000000001</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3.768</v>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>13.272</v>
+        <v>13.761</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>8.287000000000001</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>4.124</v>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>20.18862184362641</v>
+        <v>20.93246121083055</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>14.99421003112108</v>
+        <v>14.81508286892958</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>8.51520720199872</v>
@@ -3344,28 +3344,28 @@
         <v>6.661</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.782</v>
+        <v>11.127</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.623</v>
+        <v>1.603</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.195</v>
+        <v>10.938</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.679</v>
+        <v>12.851</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.889</v>
+        <v>11.103</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.137</v>
+        <v>27.365</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.428</v>
+        <v>38.902</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.638</v>
+        <v>26.676</v>
       </c>
       <c r="L48" s="1" t="inlineStr">
         <is>
@@ -3373,16 +3373,16 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>5.187</v>
+        <v>14.811</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.312</v>
+        <v>33.858</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.332</v>
+        <v>45.587</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>3.73</v>
+        <v>51.819</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>1.01</v>
@@ -5004,28 +5004,28 @@
         <v>5.631</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>5.551</v>
+        <v>5.703</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>5.31</v>
+        <v>5.337</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>13.51</v>
+        <v>13.513</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>15.971</v>
+        <v>17.086</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>17.772</v>
+        <v>18.224</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>16.585</v>
+        <v>30.105</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>29.308</v>
+        <v>41.787</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>16.857</v>
+        <v>34.988</v>
       </c>
       <c r="L75" s="1" t="inlineStr">
         <is>
@@ -5033,22 +5033,22 @@
         </is>
       </c>
       <c r="M75" s="3" t="n">
-        <v>34.562</v>
+        <v>60.144</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>34.421</v>
+        <v>49.032</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>39.985</v>
+        <v>86.523</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>55.441</v>
+        <v>102.436</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>50.236</v>
+        <v>76.193</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>58.13</v>
+        <v>82.495</v>
       </c>
     </row>
     <row r="76">
@@ -10151,7 +10151,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -15104,7 +15104,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -17587,7 +17587,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -17993,7 +17993,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -19104,7 +19104,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -20124,7 +20124,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -21647,7 +21647,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -21956,7 +21956,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -25428,7 +25428,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -76598,7 +76598,7 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E681" s="5" t="n">

--- a/output/pdf_financials_xlsx/DRX.xlsx
+++ b/output/pdf_financials_xlsx/DRX.xlsx
@@ -1152,10 +1152,10 @@
         <v>-0</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>-0</v>
+        <v>-1.116</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.827</v>
       </c>
     </row>
     <row r="14">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.339</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0.356</v>
@@ -2198,10 +2198,10 @@
         <v>0.435</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0.71</v>
+        <v>0.498</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0.336</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="29">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>13.761</v>
+        <v>14.161</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>8.188000000000001</v>
+        <v>8.526999999999999</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>4.124</v>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>20.93246121083055</v>
+        <v>21.54091877091573</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>14.81508286892958</v>
+        <v>15.42845769703988</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>8.51520720199872</v>
@@ -6509,28 +6509,28 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.356</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.391</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.362</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.307</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.321</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.361</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.394</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.367</v>
       </c>
       <c r="L100" s="1" t="inlineStr">
         <is>
@@ -6538,22 +6538,22 @@
         </is>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.449</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.498</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.498</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="101">
@@ -28967,7 +28967,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -32032,7 +32032,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -34989,7 +34989,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -37278,7 +37278,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -43777,7 +43777,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -47145,7 +47145,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -49072,7 +49072,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -50850,7 +50850,11 @@
           <t>Net financial expense (Note 21)</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E421" t="inlineStr">
         <is>
           <t>-</t>
@@ -53396,7 +53400,11 @@
           <t>Net financial expense (Note 17) 1,116</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
           <t>-</t>
@@ -76293,7 +76301,7 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E678" s="5" t="n">

--- a/output/pdf_financials_xlsx/DRX.xlsx
+++ b/output/pdf_financials_xlsx/DRX.xlsx
@@ -1312,7 +1312,7 @@
         <v>2.172</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-0.374</v>
+        <v>-2.393</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>-9.385</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>2.019</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>2.172</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.374</v>
+        <v>-2.393</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>2.566</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.007</v>
+        <v>-2.026</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>1.421811452065117</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-0.005182382859638862</v>
+        <v>-1.499929667661191</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>432.0902394106814</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0</v>
+        <v>-84.37108232344337</v>
       </c>
       <c r="L31" s="1" t="inlineStr">
         <is>
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>1.429</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.587</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>0</v>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>14.85</v>
+        <v>16.279</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>22.802</v>
+        <v>23.389</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>14.189</v>
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>9.592000000000001</v>
+        <v>8.163</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>6.661</v>
+        <v>6.074</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>11.127</v>
@@ -3850,10 +3850,10 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>0</v>
+        <v>66.88500000000001</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>68.596</v>
       </c>
       <c r="D56" s="3" t="n">
         <v>0</v>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>0</v>
+        <v>24.125</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>26.369</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>0</v>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>1.955</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>0</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.994</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0</v>
+        <v>2.949</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="D68" s="3" t="n">
         <v>0</v>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>4.681</v>
+        <v>1.732</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>5.631</v>
+        <v>2.151</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>5.703</v>
@@ -7533,28 +7533,28 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.373</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.359</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.488</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.373</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.411</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.41</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.671</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.482</v>
       </c>
       <c r="L116" s="1" t="inlineStr">
         <is>
@@ -7562,22 +7562,22 @@
         </is>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-0.361</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-0.589</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-0.698</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0</v>
+        <v>-0.72</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="R116" s="3" t="n">
-        <v>0</v>
+        <v>-3.666</v>
       </c>
     </row>
     <row r="117">
@@ -30460,7 +30460,11 @@
           <t>Acquisition of intangible assets (Note 11)</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -33359,7 +33363,11 @@
           <t>Acquisition of intangible assets (Note 8) (810)</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -36282,7 +36290,11 @@
           <t>Acquisition of intangible assets (Note 8)</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -38371,7 +38383,11 @@
           <t>Acquisition of intangible assets (Note 9)</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -44658,7 +44674,11 @@
           <t>Acquisition of intangible assets (Note 10)</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>-</t>
@@ -46252,7 +46272,11 @@
           <t>Acquisition of intangible assets (Note 11)</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>
@@ -47753,7 +47777,11 @@
           <t>Acquisition of intangible assets (Note 10)</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -64384,7 +64412,11 @@
           <t>Income (loss) before income tax (recovery) expense</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr"/>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E557" t="inlineStr">
         <is>
           <t>-</t>
@@ -64479,7 +64511,11 @@
           <t>Income tax (recovery) expense (Note 19)</t>
         </is>
       </c>
-      <c r="D558" t="inlineStr"/>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E558" t="inlineStr">
         <is>
           <t>-</t>
